--- a/artfynd/A 37932-2022 artfynd.xlsx
+++ b/artfynd/A 37932-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>116588910</v>
+        <v>125449135</v>
       </c>
       <c r="B2" t="n">
-        <v>56491</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57813</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>100136</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>J.R. Forster, 1772</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -757,22 +752,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-05</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-05</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>21:50</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>I byn Trollamåla Långasjö</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,32 +799,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125449135</v>
+        <v>116588910</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100136</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -876,27 +876,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>21:50</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>21:50</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>I byn Trollamåla Långasjö</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,6 +915,111 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>66696443</v>
+      </c>
+      <c r="B4" t="n">
+        <v>107908</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219955</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Slåttergubbe</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Arnica montana</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Trollasjömåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>529459</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6269874</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Emmaboda</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Långasjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2017-07-13</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2017-07-13</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Enstaka plantor.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Aron Edman</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Aron Edman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37932-2022 artfynd.xlsx
+++ b/artfynd/A 37932-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -796,6 +801,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125449135</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -915,6 +925,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116588910</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,8 +1035,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66696443</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>